--- a/activitereeldirect.xlsx
+++ b/activitereeldirect.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FA9BC3-2894-4D71-A464-74257C275A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE24AF0F-0E11-4056-AC56-4D65E90EB418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{52F3EE67-8AA3-4B10-A5A9-DE88DE815FD5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="103">
   <si>
     <t>N°commande</t>
   </si>
@@ -195,6 +195,156 @@
   </si>
   <si>
     <t>janvier</t>
+  </si>
+  <si>
+    <t>26408585</t>
+  </si>
+  <si>
+    <t>26609350</t>
+  </si>
+  <si>
+    <t>26381024</t>
+  </si>
+  <si>
+    <t>26386581</t>
+  </si>
+  <si>
+    <t>RENNES MOTOCULTURE SASU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83201 10                 </t>
+  </si>
+  <si>
+    <t>83201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLOY WHEEL CLEANER 5L NETTOYANT JANTES                      </t>
+  </si>
+  <si>
+    <t>PONTORSON</t>
+  </si>
+  <si>
+    <t>50170</t>
+  </si>
+  <si>
+    <t>16 RUE DES COLVERTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84335 27                 </t>
+  </si>
+  <si>
+    <t>84335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT 1 GRAISSE C1200 PRESSURE PACK + 1 BROSSE APPLICATEUR     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86466 22                 </t>
+  </si>
+  <si>
+    <t>86466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NETTOYANT POLLUTION TRAFFIC FILM REMOVER                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86663 16                 </t>
+  </si>
+  <si>
+    <t>86663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2K SUPER BOND 10G +3 BUSES MEL                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86791 28                 </t>
+  </si>
+  <si>
+    <t>86791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAPID BOND SE BLANC/AMBRE 7MN                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86847 22                 </t>
+  </si>
+  <si>
+    <t>86847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAISSE BLEU 1L - POT 1KG                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86850 10                 </t>
+  </si>
+  <si>
+    <t>86850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAPID BOND BLACK 5 MIN                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">86924 24                 </t>
+  </si>
+  <si>
+    <t>86924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPER BOND GEL - 20 GR                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">87091 00                 </t>
+  </si>
+  <si>
+    <t>87091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHIFFON DE FINITION - 40 X 40 PAQUET DE 3                    </t>
+  </si>
+  <si>
+    <t>26408236</t>
+  </si>
+  <si>
+    <t>26608897</t>
+  </si>
+  <si>
+    <t>568373</t>
+  </si>
+  <si>
+    <t>RIVIERE SYNERGIE SARL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85238 10                 </t>
+  </si>
+  <si>
+    <t>85238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUT AND DRILL FLUID 2 FLUIDE D E COUPE                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDE 56099                </t>
+  </si>
+  <si>
+    <t>LISIEUX CEDEX</t>
+  </si>
+  <si>
+    <t>14103</t>
+  </si>
+  <si>
+    <t>31 RUE FERDINAND DAULNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87485 10                 </t>
+  </si>
+  <si>
+    <t>87485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFT SURFACE CLEANER - STANDARD                              </t>
+  </si>
+  <si>
+    <t>Mars</t>
   </si>
 </sst>
 </file>
@@ -570,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA07812-0C85-468D-8FD3-167ED09F5A69}">
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.35">
@@ -857,6 +1007,787 @@
         <v>52</v>
       </c>
     </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46107</v>
+      </c>
+      <c r="G5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>85.68</v>
+      </c>
+      <c r="L5">
+        <v>85.68</v>
+      </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="1">
+        <v>46107</v>
+      </c>
+      <c r="P5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" t="s">
+        <v>33</v>
+      </c>
+      <c r="S5" t="s">
+        <v>34</v>
+      </c>
+      <c r="T5" t="s">
+        <v>61</v>
+      </c>
+      <c r="U5" t="s">
+        <v>62</v>
+      </c>
+      <c r="V5" t="s">
+        <v>63</v>
+      </c>
+      <c r="W5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46107</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>61.07</v>
+      </c>
+      <c r="L6">
+        <v>61.07</v>
+      </c>
+      <c r="M6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="1">
+        <v>46107</v>
+      </c>
+      <c r="P6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S6" t="s">
+        <v>34</v>
+      </c>
+      <c r="T6" t="s">
+        <v>61</v>
+      </c>
+      <c r="U6" t="s">
+        <v>62</v>
+      </c>
+      <c r="V6" t="s">
+        <v>63</v>
+      </c>
+      <c r="W6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46107</v>
+      </c>
+      <c r="G7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>247.96</v>
+      </c>
+      <c r="L7">
+        <v>247.96</v>
+      </c>
+      <c r="M7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="1">
+        <v>46107</v>
+      </c>
+      <c r="P7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" t="s">
+        <v>33</v>
+      </c>
+      <c r="S7" t="s">
+        <v>34</v>
+      </c>
+      <c r="T7" t="s">
+        <v>61</v>
+      </c>
+      <c r="U7" t="s">
+        <v>62</v>
+      </c>
+      <c r="V7" t="s">
+        <v>63</v>
+      </c>
+      <c r="W7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46107</v>
+      </c>
+      <c r="G8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
+        <v>35.47</v>
+      </c>
+      <c r="L8">
+        <v>70.94</v>
+      </c>
+      <c r="M8" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="1">
+        <v>46107</v>
+      </c>
+      <c r="P8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T8" t="s">
+        <v>61</v>
+      </c>
+      <c r="U8" t="s">
+        <v>62</v>
+      </c>
+      <c r="V8" t="s">
+        <v>63</v>
+      </c>
+      <c r="W8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46107</v>
+      </c>
+      <c r="G9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>32.86</v>
+      </c>
+      <c r="L9">
+        <v>65.72</v>
+      </c>
+      <c r="M9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" s="1">
+        <v>46107</v>
+      </c>
+      <c r="P9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" t="s">
+        <v>33</v>
+      </c>
+      <c r="S9" t="s">
+        <v>34</v>
+      </c>
+      <c r="T9" t="s">
+        <v>61</v>
+      </c>
+      <c r="U9" t="s">
+        <v>62</v>
+      </c>
+      <c r="V9" t="s">
+        <v>63</v>
+      </c>
+      <c r="W9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46107</v>
+      </c>
+      <c r="G10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10">
+        <v>41.8</v>
+      </c>
+      <c r="L10">
+        <v>83.6</v>
+      </c>
+      <c r="M10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" s="1">
+        <v>46107</v>
+      </c>
+      <c r="P10" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R10" t="s">
+        <v>33</v>
+      </c>
+      <c r="S10" t="s">
+        <v>34</v>
+      </c>
+      <c r="T10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V10" t="s">
+        <v>63</v>
+      </c>
+      <c r="W10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46107</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" t="s">
+        <v>81</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>30.12</v>
+      </c>
+      <c r="L11">
+        <v>60.24</v>
+      </c>
+      <c r="M11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" s="1">
+        <v>46107</v>
+      </c>
+      <c r="P11" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" t="s">
+        <v>33</v>
+      </c>
+      <c r="S11" t="s">
+        <v>34</v>
+      </c>
+      <c r="T11" t="s">
+        <v>61</v>
+      </c>
+      <c r="U11" t="s">
+        <v>62</v>
+      </c>
+      <c r="V11" t="s">
+        <v>63</v>
+      </c>
+      <c r="W11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46107</v>
+      </c>
+      <c r="G12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>18.52</v>
+      </c>
+      <c r="L12">
+        <v>18.52</v>
+      </c>
+      <c r="M12" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" s="1">
+        <v>46107</v>
+      </c>
+      <c r="P12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12" t="s">
+        <v>33</v>
+      </c>
+      <c r="S12" t="s">
+        <v>34</v>
+      </c>
+      <c r="T12" t="s">
+        <v>61</v>
+      </c>
+      <c r="U12" t="s">
+        <v>62</v>
+      </c>
+      <c r="V12" t="s">
+        <v>63</v>
+      </c>
+      <c r="W12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="1">
+        <v>46107</v>
+      </c>
+      <c r="G13" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>25.44</v>
+      </c>
+      <c r="L13">
+        <v>50.88</v>
+      </c>
+      <c r="M13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N13" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" s="1">
+        <v>46107</v>
+      </c>
+      <c r="P13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" t="s">
+        <v>33</v>
+      </c>
+      <c r="S13" t="s">
+        <v>34</v>
+      </c>
+      <c r="T13" t="s">
+        <v>61</v>
+      </c>
+      <c r="U13" t="s">
+        <v>62</v>
+      </c>
+      <c r="V13" t="s">
+        <v>63</v>
+      </c>
+      <c r="W13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46105</v>
+      </c>
+      <c r="G14" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <v>12.8</v>
+      </c>
+      <c r="L14">
+        <v>153.6</v>
+      </c>
+      <c r="M14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N14" t="s">
+        <v>30</v>
+      </c>
+      <c r="O14" s="1">
+        <v>46104</v>
+      </c>
+      <c r="P14" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" t="s">
+        <v>33</v>
+      </c>
+      <c r="S14" t="s">
+        <v>34</v>
+      </c>
+      <c r="T14" t="s">
+        <v>96</v>
+      </c>
+      <c r="U14" t="s">
+        <v>97</v>
+      </c>
+      <c r="V14" t="s">
+        <v>98</v>
+      </c>
+      <c r="W14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="1">
+        <v>46105</v>
+      </c>
+      <c r="G15" t="s">
+        <v>99</v>
+      </c>
+      <c r="H15" t="s">
+        <v>100</v>
+      </c>
+      <c r="I15" t="s">
+        <v>101</v>
+      </c>
+      <c r="J15">
+        <v>12</v>
+      </c>
+      <c r="K15">
+        <v>15.75</v>
+      </c>
+      <c r="L15">
+        <v>189</v>
+      </c>
+      <c r="M15" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="1">
+        <v>46104</v>
+      </c>
+      <c r="P15" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" t="s">
+        <v>33</v>
+      </c>
+      <c r="S15" t="s">
+        <v>34</v>
+      </c>
+      <c r="T15" t="s">
+        <v>96</v>
+      </c>
+      <c r="U15" t="s">
+        <v>97</v>
+      </c>
+      <c r="V15" t="s">
+        <v>98</v>
+      </c>
+      <c r="W15" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
